--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_22-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_22-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6CCAB7-93CC-47DE-A371-2D621760BBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35EE851-B752-420E-AB43-A0FD14A75A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="1905" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="195" windowWidth="21600" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="266">
   <si>
     <t>SKU</t>
   </si>
@@ -451,9 +451,6 @@
     <t>£836.5</t>
   </si>
   <si>
-    <t>£27.76</t>
-  </si>
-  <si>
     <t>£23.13</t>
   </si>
   <si>
@@ -487,18 +484,6 @@
     <t>£93.69</t>
   </si>
   <si>
-    <t>£152.35</t>
-  </si>
-  <si>
-    <t>£146.92</t>
-  </si>
-  <si>
-    <t>£535.35</t>
-  </si>
-  <si>
-    <t>£428.28</t>
-  </si>
-  <si>
     <t>£15.25</t>
   </si>
   <si>
@@ -782,6 +767,57 @@
   </si>
   <si>
     <t>£711.4</t>
+  </si>
+  <si>
+    <t>£18.10</t>
+  </si>
+  <si>
+    <t>£22.39</t>
+  </si>
+  <si>
+    <t>£23.42</t>
+  </si>
+  <si>
+    <t>£30.08</t>
+  </si>
+  <si>
+    <t>£32.99</t>
+  </si>
+  <si>
+    <t>£36.74</t>
+  </si>
+  <si>
+    <t>£40.42</t>
+  </si>
+  <si>
+    <t>£39.91</t>
+  </si>
+  <si>
+    <t>£49.61</t>
+  </si>
+  <si>
+    <t>£59.61</t>
+  </si>
+  <si>
+    <t>£60.64</t>
+  </si>
+  <si>
+    <t>£59.79</t>
+  </si>
+  <si>
+    <t>£106.99</t>
+  </si>
+  <si>
+    <t>£91.99</t>
+  </si>
+  <si>
+    <t>£594.55</t>
+  </si>
+  <si>
+    <t>£659.55</t>
+  </si>
+  <si>
+    <t>£559.96</t>
   </si>
 </sst>
 </file>
@@ -1216,19 +1252,19 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H2" t="s">
         <v>67</v>
@@ -1252,16 +1288,16 @@
         <v>143</v>
       </c>
       <c r="O2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="P2" t="s">
         <v>88</v>
       </c>
       <c r="Q2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="R2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1281,10 +1317,10 @@
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
         <v>68</v>
@@ -1308,16 +1344,16 @@
         <v>144</v>
       </c>
       <c r="O3" t="s">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="P3" t="s">
         <v>88</v>
       </c>
       <c r="Q3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="R3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1328,19 +1364,19 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H4" t="s">
         <v>69</v>
@@ -1364,16 +1400,16 @@
         <v>145</v>
       </c>
       <c r="O4" t="s">
-        <v>146</v>
+        <v>250</v>
       </c>
       <c r="P4" t="s">
         <v>88</v>
       </c>
       <c r="Q4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="R4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1384,19 +1420,19 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
@@ -1420,16 +1456,16 @@
         <v>146</v>
       </c>
       <c r="O5" t="s">
-        <v>147</v>
+        <v>251</v>
       </c>
       <c r="P5" t="s">
         <v>88</v>
       </c>
       <c r="Q5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="R5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1440,19 +1476,19 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H6" t="s">
         <v>71</v>
@@ -1476,16 +1512,16 @@
         <v>147</v>
       </c>
       <c r="O6" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="P6" t="s">
         <v>88</v>
       </c>
       <c r="Q6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1496,19 +1532,19 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
         <v>72</v>
@@ -1529,19 +1565,19 @@
         <v>133</v>
       </c>
       <c r="N7" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="O7" t="s">
-        <v>88</v>
+        <v>253</v>
       </c>
       <c r="P7" t="s">
         <v>88</v>
       </c>
       <c r="Q7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="R7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1552,19 +1588,19 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H8" t="s">
         <v>72</v>
@@ -1588,16 +1624,16 @@
         <v>148</v>
       </c>
       <c r="O8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="P8" t="s">
         <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="R8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1608,19 +1644,19 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H9" t="s">
         <v>73</v>
@@ -1644,16 +1680,16 @@
         <v>149</v>
       </c>
       <c r="O9" t="s">
-        <v>150</v>
+        <v>254</v>
       </c>
       <c r="P9" t="s">
         <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="R9" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1664,19 +1700,19 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F10" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G10" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H10" t="s">
         <v>74</v>
@@ -1697,19 +1733,19 @@
         <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="O10" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="P10" t="s">
         <v>88</v>
       </c>
       <c r="Q10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="R10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1720,19 +1756,19 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H11" t="s">
         <v>75</v>
@@ -1756,16 +1792,16 @@
         <v>150</v>
       </c>
       <c r="O11" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="P11" t="s">
         <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="R11" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1776,19 +1812,19 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E12" t="s">
         <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H12" t="s">
         <v>66</v>
@@ -1809,16 +1845,16 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="O12" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s">
         <v>88</v>
       </c>
       <c r="Q12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="R12" t="s">
         <v>66</v>
@@ -1832,19 +1868,19 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G13" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H13" t="s">
         <v>76</v>
@@ -1865,19 +1901,19 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O13" t="s">
-        <v>153</v>
+        <v>257</v>
       </c>
       <c r="P13" t="s">
         <v>88</v>
       </c>
       <c r="Q13" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="R13" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1888,19 +1924,19 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E14" t="s">
         <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H14" t="s">
         <v>77</v>
@@ -1921,16 +1957,16 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O14" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="P14" t="s">
         <v>88</v>
       </c>
       <c r="Q14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="R14" t="s">
         <v>66</v>
@@ -1944,19 +1980,19 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
         <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G15" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H15" t="s">
         <v>78</v>
@@ -1980,13 +2016,13 @@
         <v>153</v>
       </c>
       <c r="O15" t="s">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="P15" t="s">
         <v>88</v>
       </c>
       <c r="Q15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="R15" t="s">
         <v>66</v>
@@ -2000,19 +2036,19 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G16" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H16" t="s">
         <v>79</v>
@@ -2033,19 +2069,19 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="P16" t="s">
         <v>88</v>
       </c>
       <c r="Q16" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="R16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2056,7 +2092,7 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
         <v>88</v>
@@ -2112,10 +2148,10 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
@@ -2124,7 +2160,7 @@
         <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H18" t="s">
         <v>66</v>
@@ -2145,10 +2181,10 @@
         <v>66</v>
       </c>
       <c r="N18" t="s">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="O18" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="P18" t="s">
         <v>88</v>
@@ -2157,7 +2193,7 @@
         <v>66</v>
       </c>
       <c r="R18" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2168,10 +2204,10 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E19" t="s">
         <v>66</v>
@@ -2180,7 +2216,7 @@
         <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H19" t="s">
         <v>66</v>
@@ -2201,10 +2237,10 @@
         <v>66</v>
       </c>
       <c r="N19" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="O19" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="P19" t="s">
         <v>88</v>
@@ -2213,7 +2249,7 @@
         <v>66</v>
       </c>
       <c r="R19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2224,10 +2260,10 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E20" t="s">
         <v>66</v>
@@ -2280,10 +2316,10 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
         <v>66</v>
@@ -2336,10 +2372,10 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E22" t="s">
         <v>66</v>
@@ -2392,19 +2428,19 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F23" t="s">
         <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H23" t="s">
         <v>80</v>
@@ -2416,7 +2452,7 @@
         <v>66</v>
       </c>
       <c r="K23" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s">
         <v>66</v>
@@ -2425,10 +2461,10 @@
         <v>142</v>
       </c>
       <c r="N23" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="P23" t="s">
         <v>66</v>
@@ -2437,7 +2473,7 @@
         <v>66</v>
       </c>
       <c r="R23" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2448,19 +2484,19 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H24" t="s">
         <v>81</v>
@@ -2472,7 +2508,7 @@
         <v>66</v>
       </c>
       <c r="K24" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s">
         <v>66</v>
@@ -2481,10 +2517,10 @@
         <v>88</v>
       </c>
       <c r="N24" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="P24" t="s">
         <v>66</v>
@@ -2493,7 +2529,7 @@
         <v>66</v>
       </c>
       <c r="R24" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2504,19 +2540,19 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F25" t="s">
         <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H25" t="s">
         <v>82</v>
@@ -2537,10 +2573,10 @@
         <v>88</v>
       </c>
       <c r="N25" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="P25" t="s">
         <v>66</v>
@@ -2549,7 +2585,7 @@
         <v>66</v>
       </c>
       <c r="R25" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
